--- a/reports/pdf_rolling5_20260901.xlsx
+++ b/reports/pdf_rolling5_20260901.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,589억   ·   현금 70억(1.5%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 11종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,589억   ·   현금 35억(0.8%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 11종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1226,7 +1226,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,806억   ·   현금 25억(0.6%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 5종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,806억   ·   현금 12억(0.3%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1503,7 +1503,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,587억   ·   현금 90억(3.4%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 7종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,587억   ·   현금 45억(1.7%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 7종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1768,23 +1768,23 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스  (신규)</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>3299040000</v>
+        <v>5623680000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>1.04%→2.26%</t>
+          <t>0.00%→2.20%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>15→35</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -1812,23 +1812,23 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>5623680000</v>
+        <v>3299040000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.20%</t>
+          <t>1.04%→2.26%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>0→20</t>
+          <t>15→35</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -1956,7 +1956,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,175억   ·   현금 54억(2.4%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 7종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,175억   ·   현금 27억(1.2%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -2289,7 +2289,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 3억(1.1%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 14종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 2억(0.6%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 14종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
@@ -2510,23 +2510,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>26</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>62431200</v>
+        <v>101462400</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>3.01%→3.23%</t>
+          <t>0.74%→1.11%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>348→374</t>
+          <t>53→79</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2554,23 +2554,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>26</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>101462400</v>
+        <v>62431200</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.74%→1.11%</t>
+          <t>3.01%→3.23%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>53→79</t>
+          <t>348→374</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2663,23 +2663,23 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-89856000</v>
+        <v>-80280000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>3.46%→3.14%</t>
+          <t>2.74%→2.46%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>
@@ -2707,23 +2707,23 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-80280000</v>
+        <v>-89856000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.74%→2.46%</t>
+          <t>3.46%→3.14%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2774,23 +2774,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>36590400</v>
+        <v>33112800</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.79%→0.92%</t>
+          <t>1.00%→1.12%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>59→66</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2802,23 +2802,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>33112800</v>
+        <v>36590400</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.12%</t>
+          <t>0.79%→0.92%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>59→66</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>
@@ -2858,23 +2858,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>2129760</v>
+        <v>35640000</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>7.61%→7.62%</t>
+          <t>0.09%→0.21%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>2,981→2,984</t>
+          <t>2→5</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -2886,23 +2886,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>35640000</v>
+        <v>2129760</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.21%</t>
+          <t>7.61%→7.62%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>2→5</t>
+          <t>2,981→2,984</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>
@@ -2914,7 +2914,7 @@
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 544억   ·   현금 8억(1.5%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 544억   ·   현금 4억(0.7%)      오늘 2026-09-01  vs  5일전 2026-08-25      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B72" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260901.xlsx
+++ b/reports/pdf_rolling5_20260901.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2285568000</v>
+        <v>426240000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.48%→1.00%</t>
+          <t>1.15%→1.32%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>9→18</t>
+          <t>118→127</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>426240000</v>
+        <v>2285568000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.32%</t>
+          <t>0.48%→1.00%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>118→127</t>
+          <t>9→18</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1147,23 +1147,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-395264000</v>
+        <v>-98304000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.33%</t>
+          <t>0.63%→0.63%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1175,23 +1175,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-98304000</v>
+        <v>-395264000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.63%</t>
+          <t>1.56%→1.33%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -1768,23 +1768,23 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5623680000</v>
+        <v>3299040000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.20%</t>
+          <t>1.04%→2.26%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>0→20</t>
+          <t>15→35</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -1812,23 +1812,23 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스  (신규)</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3299040000</v>
+        <v>5623680000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1.04%→2.26%</t>
+          <t>0.00%→2.20%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>15→35</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2663,23 +2663,23 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-80280000</v>
+        <v>-89856000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.74%→2.46%</t>
+          <t>3.46%→3.14%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2707,23 +2707,23 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-89856000</v>
+        <v>-80280000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>3.46%→3.14%</t>
+          <t>2.74%→2.46%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>
@@ -2774,23 +2774,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>33112800</v>
+        <v>36590400</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.12%</t>
+          <t>0.79%→0.92%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>59→66</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2802,23 +2802,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>36590400</v>
+        <v>33112800</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>0.79%→0.92%</t>
+          <t>1.00%→1.12%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>59→66</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>
@@ -2858,23 +2858,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>35640000</v>
+        <v>2129760</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.21%</t>
+          <t>7.61%→7.62%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>2→5</t>
+          <t>2,981→2,984</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -2886,23 +2886,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2129760</v>
+        <v>35640000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>7.61%→7.62%</t>
+          <t>0.09%→0.21%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>2,981→2,984</t>
+          <t>2→5</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260901.xlsx
+++ b/reports/pdf_rolling5_20260901.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>426240000</v>
+        <v>2285568000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.32%</t>
+          <t>0.48%→1.00%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>118→127</t>
+          <t>9→18</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2285568000</v>
+        <v>426240000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.48%→1.00%</t>
+          <t>1.15%→1.32%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>9→18</t>
+          <t>118→127</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1147,23 +1147,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-98304000</v>
+        <v>-395264000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.63%</t>
+          <t>1.56%→1.33%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -1175,23 +1175,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-395264000</v>
+        <v>-98304000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.33%</t>
+          <t>0.63%→0.63%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1768,23 +1768,23 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스  (신규)</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>3299040000</v>
+        <v>5623680000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>1.04%→2.26%</t>
+          <t>0.00%→2.20%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>15→35</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -1812,23 +1812,23 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>5623680000</v>
+        <v>3299040000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.20%</t>
+          <t>1.04%→2.26%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>0→20</t>
+          <t>15→35</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2510,23 +2510,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>26</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>101462400</v>
+        <v>62431200</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.74%→1.11%</t>
+          <t>3.01%→3.23%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>53→79</t>
+          <t>348→374</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2554,23 +2554,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>26</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>62431200</v>
+        <v>101462400</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>3.01%→3.23%</t>
+          <t>0.74%→1.11%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>348→374</t>
+          <t>53→79</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2663,23 +2663,23 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-89856000</v>
+        <v>-80280000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>3.46%→3.14%</t>
+          <t>2.74%→2.46%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>
@@ -2707,23 +2707,23 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-80280000</v>
+        <v>-89856000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.74%→2.46%</t>
+          <t>3.46%→3.14%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2858,23 +2858,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>2129760</v>
+        <v>35640000</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>7.61%→7.62%</t>
+          <t>0.09%→0.21%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>2,981→2,984</t>
+          <t>2→5</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -2886,23 +2886,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>35640000</v>
+        <v>2129760</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.21%</t>
+          <t>7.61%→7.62%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>2→5</t>
+          <t>2,981→2,984</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260901.xlsx
+++ b/reports/pdf_rolling5_20260901.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2285568000</v>
+        <v>426240000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.48%→1.00%</t>
+          <t>1.15%→1.32%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>9→18</t>
+          <t>118→127</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>426240000</v>
+        <v>2285568000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.32%</t>
+          <t>0.48%→1.00%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>118→127</t>
+          <t>9→18</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1147,23 +1147,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-395264000</v>
+        <v>-98304000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.33%</t>
+          <t>0.63%→0.63%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1175,23 +1175,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-98304000</v>
+        <v>-395264000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.63%</t>
+          <t>1.56%→1.33%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -1768,23 +1768,23 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5623680000</v>
+        <v>3299040000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.20%</t>
+          <t>1.04%→2.26%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>0→20</t>
+          <t>15→35</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -1812,23 +1812,23 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스  (신규)</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>3299040000</v>
+        <v>5623680000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1.04%→2.26%</t>
+          <t>0.00%→2.20%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>15→35</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2858,23 +2858,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>35640000</v>
+        <v>2129760</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.21%</t>
+          <t>7.61%→7.62%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>2→5</t>
+          <t>2,981→2,984</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -2886,23 +2886,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2129760</v>
+        <v>35640000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>7.61%→7.62%</t>
+          <t>0.09%→0.21%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>2,981→2,984</t>
+          <t>2→5</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>
